--- a/Outputs/Scenarios/PtX_demand_SI_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SI_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.000955407017199607</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005711452919564417</v>
+        <v>0.0006187407329528117</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0001285076906901994</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001142290583912883</v>
+        <v>0.001028061525521595</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>1.376579788500048e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0001903817639854806</v>
+        <v>0.0001285076906901994</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001414363771599922</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003082818049279434</v>
+        <v>0.003339719553386053</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0006936340610878728</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.006165636098558869</v>
+        <v>0.005549072488702982</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>7.444019850525905e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001027606016426478</v>
+        <v>0.0006936340610878728</v>
       </c>
     </row>
     <row r="43">
